--- a/add-ext-deleted/ig/all-profiles.xlsx
+++ b/add-ext-deleted/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T10:37:32+00:00</t>
+    <t>2026-09-30T12:38:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-ext-deleted/ig/all-profiles.xlsx
+++ b/add-ext-deleted/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25199" uniqueCount="1335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25199" uniqueCount="1336">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T12:38:48+00:00</t>
+    <t>2026-09-30T12:48:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,7 +263,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}constr-cdr-isarchived-status:Lorsque l'extension PDSm_IsArchived vaut true, l'élément status doit valoir current ou superseded. {extension.where(url = 'https://interop.esante.gouv.fr/ig/fhir/pdsm/StructureDefinition/pdsm-ext-is-archived' and value = true).exists() implies (status = 'current' or status = 'superseded')}constr-cdr-isdeleted-status:Lorsque l'extension PDSm_IsDeleted vaut true, l'élément status doit valoir superseded. {extension.where(url = 'https://interop.esante.gouv.fr/ig/fhir/pdsm/StructureDefinition/pdsm-ext-is-deleted' and value = true).exists() implies status = 'superseded'}</t>
   </si>
   <si>
     <t>DocumentReference.id</t>
@@ -3869,6 +3869,10 @@
   </si>
   <si>
     <t>https://profiles.ihe.net/ITI/MHD/StructureDefinition/IHE.MHD.SimplifiedPublish.DocumentReference</t>
+  </si>
+  <si>
+    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -5838,7 +5842,7 @@
         <v>2</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="197">
@@ -5846,7 +5850,7 @@
         <v>4</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="198">
@@ -5862,7 +5866,7 @@
         <v>8</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="200">
@@ -5870,7 +5874,7 @@
         <v>10</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="201">
@@ -5924,7 +5928,7 @@
         <v>23</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="208">
@@ -5968,7 +5972,7 @@
         <v>33</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="214">
@@ -71902,7 +71906,7 @@
         <v>75</v>
       </c>
       <c r="AK631" t="s" s="2">
-        <v>82</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="632">
@@ -73408,7 +73412,7 @@
         <v>105</v>
       </c>
       <c r="N646" t="s" s="2">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="O646" t="s" s="2">
         <v>107</v>
@@ -73840,7 +73844,7 @@
         <v>75</v>
       </c>
       <c r="T650" t="s" s="2">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="U650" t="s" s="2">
         <v>75</v>
@@ -73858,10 +73862,10 @@
         <v>216</v>
       </c>
       <c r="Z650" t="s" s="2">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="AA650" t="s" s="2">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="AB650" t="s" s="2">
         <v>75</v>
@@ -74033,7 +74037,7 @@
         <v>225</v>
       </c>
       <c r="M652" t="s" s="2">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="N652" t="s" s="2">
         <v>226</v>
@@ -74239,7 +74243,7 @@
         <v>239</v>
       </c>
       <c r="M654" t="s" s="2">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="N654" t="s" s="2">
         <v>241</v>
@@ -74444,7 +74448,7 @@
         <v>85</v>
       </c>
       <c r="L656" t="s" s="2">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="M656" t="s" s="2">
         <v>249</v>
@@ -74762,10 +74766,10 @@
         <v>263</v>
       </c>
       <c r="M659" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="N659" t="s" s="2">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="O659" t="s" s="2">
         <v>266</v>
@@ -74830,7 +74834,7 @@
         <v>75</v>
       </c>
       <c r="AK659" t="s" s="2">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="660">
@@ -75182,7 +75186,7 @@
         <v>159</v>
       </c>
       <c r="M663" t="s" s="2">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="N663" t="s" s="2">
         <v>278</v>
@@ -75250,7 +75254,7 @@
         <v>75</v>
       </c>
       <c r="AK663" t="s" s="2">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="664">
@@ -75287,7 +75291,7 @@
         <v>283</v>
       </c>
       <c r="M664" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="N664" t="s" s="2">
         <v>285</v>
@@ -75353,7 +75357,7 @@
         <v>75</v>
       </c>
       <c r="AK664" t="s" s="2">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="665">
@@ -75390,7 +75394,7 @@
         <v>98</v>
       </c>
       <c r="M665" t="s" s="2">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="N665" t="s" s="2">
         <v>289</v>
@@ -75602,7 +75606,7 @@
         <v>263</v>
       </c>
       <c r="M667" t="s" s="2">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="N667" t="s" s="2">
         <v>300</v>
@@ -76541,7 +76545,7 @@
         <v>325</v>
       </c>
       <c r="M676" t="s" s="2">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="N676" t="s" s="2">
         <v>327</v>
@@ -76648,7 +76652,7 @@
         <v>332</v>
       </c>
       <c r="M677" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="N677" t="s" s="2">
         <v>334</v>
@@ -77074,7 +77078,7 @@
         <v>360</v>
       </c>
       <c r="M681" t="s" s="2">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="N681" t="s" s="2">
         <v>362</v>
@@ -78077,7 +78081,7 @@
         <v>75</v>
       </c>
       <c r="AK690" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="691">
@@ -78182,7 +78186,7 @@
         <v>75</v>
       </c>
       <c r="AK691" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="692">
@@ -78395,7 +78399,7 @@
     </row>
     <row r="694">
       <c r="A694" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B694" t="s" s="2">
         <v>1103</v>
@@ -78498,7 +78502,7 @@
     </row>
     <row r="695">
       <c r="A695" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B695" t="s" s="2">
         <v>1106</v>
@@ -78603,7 +78607,7 @@
     </row>
     <row r="696">
       <c r="A696" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B696" t="s" s="2">
         <v>1107</v>
@@ -78706,7 +78710,7 @@
     </row>
     <row r="697">
       <c r="A697" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B697" t="s" s="2">
         <v>1108</v>
@@ -78809,7 +78813,7 @@
     </row>
     <row r="698">
       <c r="A698" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B698" t="s" s="2">
         <v>1109</v>
@@ -78914,7 +78918,7 @@
     </row>
     <row r="699">
       <c r="A699" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B699" t="s" s="2">
         <v>1110</v>
@@ -79019,7 +79023,7 @@
     </row>
     <row r="700">
       <c r="A700" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B700" t="s" s="2">
         <v>1111</v>
@@ -79124,7 +79128,7 @@
     </row>
     <row r="701">
       <c r="A701" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B701" t="s" s="2">
         <v>1112</v>
@@ -79229,7 +79233,7 @@
     </row>
     <row r="702">
       <c r="A702" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B702" t="s" s="2">
         <v>1113</v>
@@ -79334,7 +79338,7 @@
     </row>
     <row r="703">
       <c r="A703" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B703" t="s" s="2">
         <v>1114</v>
@@ -79439,7 +79443,7 @@
     </row>
     <row r="704">
       <c r="A704" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B704" t="s" s="2">
         <v>1115</v>
@@ -79544,7 +79548,7 @@
     </row>
     <row r="705">
       <c r="A705" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B705" t="s" s="2">
         <v>1116</v>
@@ -79649,7 +79653,7 @@
     </row>
     <row r="706">
       <c r="A706" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B706" t="s" s="2">
         <v>1117</v>
@@ -79754,7 +79758,7 @@
     </row>
     <row r="707">
       <c r="A707" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B707" t="s" s="2">
         <v>1118</v>
@@ -79859,7 +79863,7 @@
     </row>
     <row r="708">
       <c r="A708" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B708" t="s" s="2">
         <v>1119</v>
@@ -79891,7 +79895,7 @@
         <v>176</v>
       </c>
       <c r="M708" t="s" s="2">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="N708" t="s" s="2">
         <v>178</v>
@@ -79964,7 +79968,7 @@
     </row>
     <row r="709">
       <c r="A709" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B709" t="s" s="2">
         <v>1121</v>
@@ -79978,7 +79982,7 @@
       </c>
       <c r="F709" s="2"/>
       <c r="G709" t="s" s="2">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H709" t="s" s="2">
         <v>77</v>
@@ -80065,7 +80069,7 @@
     </row>
     <row r="710">
       <c r="A710" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B710" t="s" s="2">
         <v>1122</v>
@@ -80099,7 +80103,7 @@
         <v>1124</v>
       </c>
       <c r="M710" t="s" s="2">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="N710" t="s" s="2">
         <v>1126</v>
@@ -80165,18 +80169,18 @@
         <v>190</v>
       </c>
       <c r="AK710" t="s" s="2">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B711" t="s" s="2">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="C711" t="s" s="2">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="D711" s="2"/>
       <c r="E711" t="s" s="2">
@@ -80273,13 +80277,13 @@
     </row>
     <row r="712">
       <c r="A712" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B712" t="s" s="2">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="C712" t="s" s="2">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="D712" s="2"/>
       <c r="E712" t="s" s="2">
@@ -80376,13 +80380,13 @@
     </row>
     <row r="713">
       <c r="A713" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B713" t="s" s="2">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="C713" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="D713" s="2"/>
       <c r="E713" t="s" s="2">
@@ -80422,7 +80426,7 @@
       </c>
       <c r="R713" s="2"/>
       <c r="S713" t="s" s="2">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="T713" t="s" s="2">
         <v>75</v>
@@ -80481,13 +80485,13 @@
     </row>
     <row r="714">
       <c r="A714" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B714" t="s" s="2">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="C714" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="D714" s="2"/>
       <c r="E714" t="s" s="2">
@@ -80547,7 +80551,7 @@
       </c>
       <c r="Z714" s="2"/>
       <c r="AA714" t="s" s="2">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="AB714" t="s" s="2">
         <v>75</v>
@@ -80582,16 +80586,16 @@
     </row>
     <row r="715">
       <c r="A715" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B715" t="s" s="2">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="C715" t="s" s="2">
         <v>1121</v>
       </c>
       <c r="D715" t="s" s="2">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="E715" t="s" s="2">
         <v>75</v>
@@ -80613,13 +80617,13 @@
         <v>75</v>
       </c>
       <c r="L715" t="s" s="2">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="M715" t="s" s="2">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="N715" t="s" s="2">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="O715" s="2"/>
       <c r="P715" s="2"/>
@@ -80687,16 +80691,16 @@
     </row>
     <row r="716">
       <c r="A716" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B716" t="s" s="2">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="C716" t="s" s="2">
         <v>1121</v>
       </c>
       <c r="D716" t="s" s="2">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="E716" t="s" s="2">
         <v>75</v>
@@ -80718,13 +80722,13 @@
         <v>75</v>
       </c>
       <c r="L716" t="s" s="2">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="M716" t="s" s="2">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="N716" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="O716" s="2"/>
       <c r="P716" s="2"/>
@@ -80792,10 +80796,10 @@
     </row>
     <row r="717">
       <c r="A717" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B717" t="s" s="2">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C717" t="s" s="2">
         <v>1121</v>
@@ -80826,7 +80830,7 @@
         <v>187</v>
       </c>
       <c r="M717" t="s" s="2">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="N717" t="s" s="2">
         <v>189</v>
@@ -80897,10 +80901,10 @@
     </row>
     <row r="718">
       <c r="A718" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B718" t="s" s="2">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="C718" t="s" s="2">
         <v>1121</v>
@@ -80931,7 +80935,7 @@
         <v>193</v>
       </c>
       <c r="M718" t="s" s="2">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="N718" t="s" s="2">
         <v>195</v>
@@ -81002,16 +81006,16 @@
     </row>
     <row r="719">
       <c r="A719" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B719" t="s" s="2">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="C719" t="s" s="2">
         <v>1121</v>
       </c>
       <c r="D719" t="s" s="2">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="E719" t="s" s="2">
         <v>75</v>
@@ -81033,10 +81037,10 @@
         <v>75</v>
       </c>
       <c r="L719" t="s" s="2">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="M719" t="s" s="2">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="N719" t="s" s="2">
         <v>994</v>
@@ -81107,13 +81111,13 @@
     </row>
     <row r="720">
       <c r="A720" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B720" t="s" s="2">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="C720" t="s" s="2">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="D720" s="2"/>
       <c r="E720" t="s" s="2">
@@ -81210,13 +81214,13 @@
     </row>
     <row r="721">
       <c r="A721" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B721" t="s" s="2">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="C721" t="s" s="2">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="D721" s="2"/>
       <c r="E721" t="s" s="2">
@@ -81313,13 +81317,13 @@
     </row>
     <row r="722">
       <c r="A722" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B722" t="s" s="2">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="C722" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="D722" s="2"/>
       <c r="E722" t="s" s="2">
@@ -81418,13 +81422,13 @@
     </row>
     <row r="723">
       <c r="A723" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B723" t="s" s="2">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C723" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="D723" s="2"/>
       <c r="E723" t="s" s="2">
@@ -81521,7 +81525,7 @@
     </row>
     <row r="724">
       <c r="A724" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B724" t="s" s="2">
         <v>1127</v>
@@ -81624,7 +81628,7 @@
     </row>
     <row r="725">
       <c r="A725" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B725" t="s" s="2">
         <v>1128</v>
@@ -81725,7 +81729,7 @@
     </row>
     <row r="726">
       <c r="A726" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B726" t="s" s="2">
         <v>1131</v>
@@ -81756,10 +81760,10 @@
         <v>75</v>
       </c>
       <c r="L726" t="s" s="2">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="M726" t="s" s="2">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="N726" t="s" s="2">
         <v>1130</v>
@@ -81830,7 +81834,7 @@
     </row>
     <row r="727">
       <c r="A727" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B727" t="s" s="2">
         <v>1134</v>
@@ -81864,7 +81868,7 @@
         <v>211</v>
       </c>
       <c r="M727" t="s" s="2">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="N727" t="s" s="2">
         <v>1130</v>
@@ -81935,7 +81939,7 @@
     </row>
     <row r="728">
       <c r="A728" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B728" t="s" s="2">
         <v>1136</v>
@@ -81967,7 +81971,7 @@
         <v>159</v>
       </c>
       <c r="M728" t="s" s="2">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="N728" t="s" s="2">
         <v>1138</v>
@@ -81984,7 +81988,7 @@
         <v>75</v>
       </c>
       <c r="T728" t="s" s="2">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="U728" t="s" s="2">
         <v>75</v>
@@ -82040,7 +82044,7 @@
     </row>
     <row r="729">
       <c r="A729" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B729" t="s" s="2">
         <v>1142</v>
@@ -82072,7 +82076,7 @@
         <v>159</v>
       </c>
       <c r="M729" t="s" s="2">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="N729" t="s" s="2">
         <v>1144</v>
@@ -82147,7 +82151,7 @@
     </row>
     <row r="730">
       <c r="A730" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B730" t="s" s="2">
         <v>1150</v>
@@ -82179,7 +82183,7 @@
         <v>98</v>
       </c>
       <c r="M730" t="s" s="2">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="N730" t="s" s="2">
         <v>1152</v>
@@ -82252,7 +82256,7 @@
     </row>
     <row r="731">
       <c r="A731" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B731" t="s" s="2">
         <v>1155</v>
@@ -82284,7 +82288,7 @@
         <v>225</v>
       </c>
       <c r="M731" t="s" s="2">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="N731" t="s" s="2">
         <v>1157</v>
@@ -82303,7 +82307,7 @@
         <v>75</v>
       </c>
       <c r="T731" t="s" s="2">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="U731" t="s" s="2">
         <v>75</v>
@@ -82357,7 +82361,7 @@
     </row>
     <row r="732">
       <c r="A732" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B732" t="s" s="2">
         <v>1162</v>
@@ -82464,7 +82468,7 @@
     </row>
     <row r="733">
       <c r="A733" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B733" t="s" s="2">
         <v>1167</v>
@@ -82567,7 +82571,7 @@
     </row>
     <row r="734">
       <c r="A734" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B734" t="s" s="2">
         <v>1171</v>
@@ -82599,7 +82603,7 @@
         <v>360</v>
       </c>
       <c r="M734" t="s" s="2">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="N734" t="s" s="2">
         <v>1173</v>
@@ -82674,7 +82678,7 @@
     </row>
     <row r="735">
       <c r="A735" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B735" t="s" s="2">
         <v>1176</v>
@@ -82703,10 +82707,10 @@
         <v>85</v>
       </c>
       <c r="L735" t="s" s="2">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="M735" t="s" s="2">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="N735" t="s" s="2">
         <v>1180</v>
@@ -82781,13 +82785,13 @@
     </row>
     <row r="736">
       <c r="A736" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B736" t="s" s="2">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="C736" t="s" s="2">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="D736" s="2"/>
       <c r="E736" t="s" s="2">
@@ -82884,13 +82888,13 @@
     </row>
     <row r="737">
       <c r="A737" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B737" t="s" s="2">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="C737" t="s" s="2">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="D737" s="2"/>
       <c r="E737" t="s" s="2">
@@ -82989,16 +82993,16 @@
     </row>
     <row r="738">
       <c r="A738" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B738" t="s" s="2">
+        <v>1313</v>
+      </c>
+      <c r="C738" t="s" s="2">
         <v>1312</v>
       </c>
-      <c r="C738" t="s" s="2">
-        <v>1311</v>
-      </c>
       <c r="D738" t="s" s="2">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="E738" t="s" s="2">
         <v>75</v>
@@ -83020,13 +83024,13 @@
         <v>75</v>
       </c>
       <c r="L738" t="s" s="2">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="M738" t="s" s="2">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="N738" t="s" s="2">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="O738" s="2"/>
       <c r="P738" s="2"/>
@@ -83094,13 +83098,13 @@
     </row>
     <row r="739">
       <c r="A739" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B739" t="s" s="2">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="C739" t="s" s="2">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="D739" s="2"/>
       <c r="E739" t="s" s="2">
@@ -83197,13 +83201,13 @@
     </row>
     <row r="740">
       <c r="A740" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B740" t="s" s="2">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="C740" t="s" s="2">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="D740" s="2"/>
       <c r="E740" t="s" s="2">
@@ -83300,13 +83304,13 @@
     </row>
     <row r="741">
       <c r="A741" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B741" t="s" s="2">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="C741" t="s" s="2">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="D741" s="2"/>
       <c r="E741" t="s" s="2">
@@ -83346,7 +83350,7 @@
       </c>
       <c r="R741" s="2"/>
       <c r="S741" t="s" s="2">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="T741" t="s" s="2">
         <v>75</v>
@@ -83405,13 +83409,13 @@
     </row>
     <row r="742">
       <c r="A742" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B742" t="s" s="2">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="C742" t="s" s="2">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="D742" s="2"/>
       <c r="E742" t="s" s="2">
@@ -83434,7 +83438,7 @@
         <v>75</v>
       </c>
       <c r="L742" t="s" s="2">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="M742" t="s" s="2">
         <v>1007</v>
@@ -83508,13 +83512,13 @@
     </row>
     <row r="743">
       <c r="A743" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B743" t="s" s="2">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="C743" t="s" s="2">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="D743" s="2"/>
       <c r="E743" t="s" s="2">
@@ -83613,13 +83617,13 @@
     </row>
     <row r="744">
       <c r="A744" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B744" t="s" s="2">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="C744" t="s" s="2">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="D744" s="2"/>
       <c r="E744" t="s" s="2">
@@ -83718,13 +83722,13 @@
     </row>
     <row r="745">
       <c r="A745" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B745" t="s" s="2">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="C745" t="s" s="2">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="D745" s="2"/>
       <c r="E745" t="s" s="2">
@@ -83823,13 +83827,13 @@
     </row>
     <row r="746">
       <c r="A746" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B746" t="s" s="2">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="C746" t="s" s="2">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="D746" s="2"/>
       <c r="E746" t="s" s="2">
@@ -83928,7 +83932,7 @@
     </row>
     <row r="747">
       <c r="A747" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B747" t="s" s="2">
         <v>1183</v>
@@ -84035,7 +84039,7 @@
     </row>
     <row r="748">
       <c r="A748" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B748" t="s" s="2">
         <v>1190</v>
@@ -84067,7 +84071,7 @@
         <v>1191</v>
       </c>
       <c r="M748" t="s" s="2">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="N748" t="s" s="2">
         <v>1193</v>
@@ -84138,7 +84142,7 @@
     </row>
     <row r="749">
       <c r="A749" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B749" t="s" s="2">
         <v>1194</v>
@@ -84170,7 +84174,7 @@
         <v>263</v>
       </c>
       <c r="M749" t="s" s="2">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="N749" t="s" s="2">
         <v>1196</v>
@@ -84243,7 +84247,7 @@
     </row>
     <row r="750">
       <c r="A750" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B750" t="s" s="2">
         <v>1199</v>
@@ -84346,7 +84350,7 @@
     </row>
     <row r="751">
       <c r="A751" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B751" t="s" s="2">
         <v>1200</v>
@@ -84451,7 +84455,7 @@
     </row>
     <row r="752">
       <c r="A752" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B752" t="s" s="2">
         <v>1201</v>
@@ -84558,7 +84562,7 @@
     </row>
     <row r="753">
       <c r="A753" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B753" t="s" s="2">
         <v>1202</v>
@@ -84665,7 +84669,7 @@
     </row>
     <row r="754">
       <c r="A754" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B754" t="s" s="2">
         <v>1209</v>
@@ -84774,7 +84778,7 @@
     </row>
     <row r="755">
       <c r="A755" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B755" t="s" s="2">
         <v>1216</v>
@@ -84879,7 +84883,7 @@
     </row>
     <row r="756">
       <c r="A756" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B756" t="s" s="2">
         <v>1220</v>
@@ -84908,10 +84912,10 @@
         <v>75</v>
       </c>
       <c r="L756" t="s" s="2">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="M756" t="s" s="2">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="N756" t="s" s="2">
         <v>1223</v>
@@ -84982,7 +84986,7 @@
     </row>
     <row r="757">
       <c r="A757" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B757" t="s" s="2">
         <v>1224</v>

--- a/add-ext-deleted/ig/all-profiles.xlsx
+++ b/add-ext-deleted/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T12:48:42+00:00</t>
+    <t>2026-09-30T13:49:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,7 +263,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}constr-cdr-isarchived-status:Lorsque l'extension PDSm_IsArchived vaut true, l'élément status doit valoir current ou superseded. {extension.where(url = 'https://interop.esante.gouv.fr/ig/fhir/pdsm/StructureDefinition/pdsm-ext-is-archived' and value = true).exists() implies (status = 'current' or status = 'superseded')}constr-cdr-isdeleted-status:Lorsque l'extension PDSm_IsDeleted vaut true, l'élément status doit valoir superseded. {extension.where(url = 'https://interop.esante.gouv.fr/ig/fhir/pdsm/StructureDefinition/pdsm-ext-is-deleted' and value = true).exists() implies status = 'superseded'}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}constr-cdr-status:La valeur entered-in-error ne doit pas être utilisée pour l'élément status (cf. https://github.com/IHE/ITI.MHD/issues/274). {status != 'entered-in-error'}constr-cdr-isdeleted-status:Lorsque l'extension PDSm_IsDeleted vaut true, l'élément status doit valoir superseded. {extension.where(url = 'https://interop.esante.gouv.fr/ig/fhir/pdsm/StructureDefinition/pdsm-ext-is-deleted' and value = true).exists() implies status = 'superseded'}</t>
   </si>
   <si>
     <t>DocumentReference.id</t>

--- a/add-ext-deleted/ig/all-profiles.xlsx
+++ b/add-ext-deleted/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25199" uniqueCount="1336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25164" uniqueCount="1334">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T13:49:36+00:00</t>
+    <t>2026-09-30T15:53:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,7 +263,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}constr-cdr-status:La valeur entered-in-error ne doit pas être utilisée pour l'élément status (cf. https://github.com/IHE/ITI.MHD/issues/274). {status != 'entered-in-error'}constr-cdr-isdeleted-status:Lorsque l'extension PDSm_IsDeleted vaut true, l'élément status doit valoir superseded. {extension.where(url = 'https://interop.esante.gouv.fr/ig/fhir/pdsm/StructureDefinition/pdsm-ext-is-deleted' and value = true).exists() implies status = 'superseded'}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}constr-cdr-status:La valeur entered-in-error ne doit pas être utilisée pour l'élément status (cf. https://github.com/IHE/ITI.MHD/issues/274). {status != 'entered-in-error'}constr-cdr-isdeleted-status:Lorsque l'extension PDSm_IsDeleted vaut true, l'élément status doit valoir superseded. {extension.where(url = 'https://interop.esante.gouv.fr/ig/fhir/pdsm/StructureDefinition/pdsm-ext-is-deleted' and value = true).exists() implies status = 'superseded'}constr-cdr-isdeleted-isarchived:Une fiche supprimée logiquement (extension PDSm_IsDeleted à true) ne peut pas être archivée (extension PDSm_IsArchived à true). {extension.where(url = 'https://interop.esante.gouv.fr/ig/fhir/pdsm/StructureDefinition/pdsm-ext-is-deleted' and value = true).exists() implies extension.where(url = 'https://interop.esante.gouv.fr/ig/fhir/pdsm/StructureDefinition/pdsm-ext-is-archived' and value = true).empty()}</t>
   </si>
   <si>
     <t>DocumentReference.id</t>
@@ -623,7 +623,7 @@
     <t>Extension définie pour distinguer les fiches supprimées. Suppression logique pas physique.</t>
   </si>
   <si>
-    <t>Extension définie par le volet ANS "Volet Partage de documents de santé en mobilité" sur les ressources List et DocumentReference pour distinguer les lots de soumission et les fiches supprimées. A noter que la suppression est logique et pas physique.</t>
+    <t>Extension définie par le volet ANS "Volet Partage de documents de santé en mobilité" sur la ressource DocumentReference pour distinguer les fiches supprimées. A noter que la suppression est logique et pas physique.</t>
   </si>
   <si>
     <t>DocumentReference.modifierExtension</t>
@@ -4044,12 +4044,6 @@
   </si>
   <si>
     <t>Extension définie par ce volet pour distinguer les lots de soumission archivés des actives.</t>
-  </si>
-  <si>
-    <t>List.extension:isDeleted</t>
-  </si>
-  <si>
-    <t>Extension définie par ce volet pour distinguer les lots de soumission supprimés. Suppression logique pas physique.</t>
   </si>
   <si>
     <t>List.extension:PDSmintendedRecipient</t>
@@ -4326,7 +4320,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B215"/>
+  <dimension ref="A1:B214"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -5174,820 +5168,812 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="s" s="2">
-        <v>997</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>998</v>
+      <c r="A110" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B110" t="s" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="B111" t="s" s="1">
-        <v>1</v>
+      <c r="A111" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>1018</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>1019</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>7</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>1021</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>12</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>13</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B117" s="2"/>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B118" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>16</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>22</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>1022</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B123" s="2"/>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B124" s="2"/>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B125" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>28</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>30</v>
+        <v>578</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>578</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>1023</v>
+        <v>36</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>38</v>
+      <c r="A131" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B131" t="s" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="B132" t="s" s="1">
-        <v>1</v>
+      <c r="A132" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>1058</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>1059</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>7</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>1061</v>
+        <v>13</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>12</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>13</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B138" s="2"/>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B139" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>16</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>22</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B144" t="s" s="2">
-        <v>1062</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B144" s="2"/>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B145" s="2"/>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B146" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>28</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>30</v>
+        <v>578</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>578</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>1063</v>
+        <v>36</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B152" t="s" s="2">
-        <v>38</v>
+      <c r="A152" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B152" t="s" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="B153" t="s" s="1">
-        <v>1</v>
+      <c r="A153" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>1098</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>1099</v>
+        <v>7</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>7</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>1101</v>
+        <v>13</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>12</v>
-      </c>
-      <c r="B159" t="s" s="2">
-        <v>13</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B159" s="2"/>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B160" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>16</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>22</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B165" t="s" s="2">
-        <v>1102</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B165" s="2"/>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B166" s="2"/>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B167" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>28</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>30</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>1104</v>
+        <v>36</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B173" t="s" s="2">
-        <v>38</v>
+      <c r="A173" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B173" t="s" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="B174" t="s" s="1">
-        <v>1</v>
+      <c r="A174" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>1231</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>1232</v>
+        <v>7</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>7</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>1234</v>
+        <v>13</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>12</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>13</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B180" s="2"/>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B181" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>16</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>22</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B186" t="s" s="2">
-        <v>1235</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B186" s="2"/>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B187" s="2"/>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B188" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="B188" t="s" s="2">
+        <v>28</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>32</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>1236</v>
+        <v>36</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B194" t="s" s="2">
-        <v>38</v>
+      <c r="A194" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B194" t="s" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="B195" t="s" s="1">
-        <v>1</v>
+      <c r="A195" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B195" t="s" s="2">
+        <v>1258</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>1259</v>
+        <v>7</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>7</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>1261</v>
+        <v>13</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>12</v>
-      </c>
-      <c r="B201" t="s" s="2">
-        <v>13</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B201" s="2"/>
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B202" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="B202" t="s" s="2">
+        <v>16</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>22</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B207" t="s" s="2">
-        <v>1262</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B207" s="2"/>
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B208" s="2"/>
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B209" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="B209" t="s" s="2">
+        <v>28</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>30</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>1103</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>1263</v>
+        <v>36</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B215" t="s" s="2">
         <v>38</v>
       </c>
     </row>
@@ -5998,7 +5984,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK757"/>
+  <dimension ref="A1:AK756"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="46.0703125" customWidth="true" bestFit="true"/>
@@ -80910,7 +80896,7 @@
         <v>1121</v>
       </c>
       <c r="D718" t="s" s="2">
-        <v>192</v>
+        <v>1291</v>
       </c>
       <c r="E718" t="s" s="2">
         <v>75</v>
@@ -80920,10 +80906,10 @@
         <v>76</v>
       </c>
       <c r="H718" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I718" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J718" t="s" s="2">
         <v>75</v>
@@ -80932,13 +80918,13 @@
         <v>75</v>
       </c>
       <c r="L718" t="s" s="2">
-        <v>193</v>
+        <v>1292</v>
       </c>
       <c r="M718" t="s" s="2">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="N718" t="s" s="2">
-        <v>195</v>
+        <v>994</v>
       </c>
       <c r="O718" s="2"/>
       <c r="P718" s="2"/>
@@ -81009,14 +80995,12 @@
         <v>1258</v>
       </c>
       <c r="B719" t="s" s="2">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="C719" t="s" s="2">
-        <v>1121</v>
-      </c>
-      <c r="D719" t="s" s="2">
-        <v>1293</v>
-      </c>
+        <v>1269</v>
+      </c>
+      <c r="D719" s="2"/>
       <c r="E719" t="s" s="2">
         <v>75</v>
       </c>
@@ -81025,10 +81009,10 @@
         <v>76</v>
       </c>
       <c r="H719" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I719" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J719" t="s" s="2">
         <v>75</v>
@@ -81037,13 +81021,13 @@
         <v>75</v>
       </c>
       <c r="L719" t="s" s="2">
-        <v>1294</v>
+        <v>98</v>
       </c>
       <c r="M719" t="s" s="2">
-        <v>1295</v>
+        <v>99</v>
       </c>
       <c r="N719" t="s" s="2">
-        <v>994</v>
+        <v>100</v>
       </c>
       <c r="O719" s="2"/>
       <c r="P719" s="2"/>
@@ -81094,19 +81078,19 @@
         <v>75</v>
       </c>
       <c r="AG719" t="s" s="2">
-        <v>184</v>
+        <v>101</v>
       </c>
       <c r="AH719" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI719" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ719" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK719" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
     </row>
     <row r="720">
@@ -81114,10 +81098,10 @@
         <v>1258</v>
       </c>
       <c r="B720" t="s" s="2">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="C720" t="s" s="2">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="D720" s="2"/>
       <c r="E720" t="s" s="2">
@@ -81128,7 +81112,7 @@
         <v>76</v>
       </c>
       <c r="H720" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I720" t="s" s="2">
         <v>75</v>
@@ -81140,13 +81124,13 @@
         <v>75</v>
       </c>
       <c r="L720" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="M720" t="s" s="2">
-        <v>99</v>
+        <v>182</v>
       </c>
       <c r="N720" t="s" s="2">
-        <v>100</v>
+        <v>183</v>
       </c>
       <c r="O720" s="2"/>
       <c r="P720" s="2"/>
@@ -81185,31 +81169,31 @@
         <v>75</v>
       </c>
       <c r="AC720" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="AD720" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AE720" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF720" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AG720" t="s" s="2">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="AH720" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI720" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ720" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK720" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
     </row>
     <row r="721">
@@ -81217,10 +81201,10 @@
         <v>1258</v>
       </c>
       <c r="B721" t="s" s="2">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="C721" t="s" s="2">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="D721" s="2"/>
       <c r="E721" t="s" s="2">
@@ -81228,10 +81212,10 @@
       </c>
       <c r="F721" s="2"/>
       <c r="G721" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H721" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="I721" t="s" s="2">
         <v>75</v>
@@ -81243,22 +81227,24 @@
         <v>75</v>
       </c>
       <c r="L721" t="s" s="2">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="M721" t="s" s="2">
-        <v>182</v>
+        <v>1002</v>
       </c>
       <c r="N721" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O721" s="2"/>
+        <v>1003</v>
+      </c>
+      <c r="O721" t="s" s="2">
+        <v>1004</v>
+      </c>
       <c r="P721" s="2"/>
       <c r="Q721" t="s" s="2">
         <v>75</v>
       </c>
       <c r="R721" s="2"/>
       <c r="S721" t="s" s="2">
-        <v>75</v>
+        <v>992</v>
       </c>
       <c r="T721" t="s" s="2">
         <v>75</v>
@@ -81288,31 +81274,31 @@
         <v>75</v>
       </c>
       <c r="AC721" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AD721" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AE721" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF721" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AG721" t="s" s="2">
-        <v>111</v>
+        <v>1001</v>
       </c>
       <c r="AH721" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI721" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ721" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK721" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
     </row>
     <row r="722">
@@ -81320,10 +81306,10 @@
         <v>1258</v>
       </c>
       <c r="B722" t="s" s="2">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="C722" t="s" s="2">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="D722" s="2"/>
       <c r="E722" t="s" s="2">
@@ -81331,7 +81317,7 @@
       </c>
       <c r="F722" s="2"/>
       <c r="G722" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H722" t="s" s="2">
         <v>84</v>
@@ -81346,24 +81332,22 @@
         <v>75</v>
       </c>
       <c r="L722" t="s" s="2">
-        <v>125</v>
+        <v>253</v>
       </c>
       <c r="M722" t="s" s="2">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="N722" t="s" s="2">
-        <v>1003</v>
-      </c>
-      <c r="O722" t="s" s="2">
-        <v>1004</v>
-      </c>
+        <v>1008</v>
+      </c>
+      <c r="O722" s="2"/>
       <c r="P722" s="2"/>
       <c r="Q722" t="s" s="2">
         <v>75</v>
       </c>
       <c r="R722" s="2"/>
       <c r="S722" t="s" s="2">
-        <v>992</v>
+        <v>75</v>
       </c>
       <c r="T722" t="s" s="2">
         <v>75</v>
@@ -81405,10 +81389,10 @@
         <v>75</v>
       </c>
       <c r="AG722" t="s" s="2">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="AH722" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI722" t="s" s="2">
         <v>84</v>
@@ -81417,7 +81401,7 @@
         <v>75</v>
       </c>
       <c r="AK722" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
     </row>
     <row r="723">
@@ -81425,10 +81409,10 @@
         <v>1258</v>
       </c>
       <c r="B723" t="s" s="2">
-        <v>1299</v>
+        <v>1127</v>
       </c>
       <c r="C723" t="s" s="2">
-        <v>1276</v>
+        <v>1127</v>
       </c>
       <c r="D723" s="2"/>
       <c r="E723" t="s" s="2">
@@ -81439,25 +81423,25 @@
         <v>76</v>
       </c>
       <c r="H723" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I723" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J723" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K723" t="s" s="2">
         <v>75</v>
       </c>
       <c r="L723" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="M723" t="s" s="2">
-        <v>1007</v>
+        <v>182</v>
       </c>
       <c r="N723" t="s" s="2">
-        <v>1008</v>
+        <v>183</v>
       </c>
       <c r="O723" s="2"/>
       <c r="P723" s="2"/>
@@ -81508,19 +81492,19 @@
         <v>75</v>
       </c>
       <c r="AG723" t="s" s="2">
-        <v>1005</v>
+        <v>197</v>
       </c>
       <c r="AH723" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI723" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ723" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK723" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="724">
@@ -81528,10 +81512,10 @@
         <v>1258</v>
       </c>
       <c r="B724" t="s" s="2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="C724" t="s" s="2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="D724" s="2"/>
       <c r="E724" t="s" s="2">
@@ -81542,25 +81526,25 @@
         <v>76</v>
       </c>
       <c r="H724" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I724" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J724" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K724" t="s" s="2">
         <v>75</v>
       </c>
       <c r="L724" t="s" s="2">
-        <v>104</v>
+        <v>205</v>
       </c>
       <c r="M724" t="s" s="2">
-        <v>182</v>
+        <v>1129</v>
       </c>
       <c r="N724" t="s" s="2">
-        <v>183</v>
+        <v>1130</v>
       </c>
       <c r="O724" s="2"/>
       <c r="P724" s="2"/>
@@ -81599,19 +81583,17 @@
         <v>75</v>
       </c>
       <c r="AC724" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD724" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="AD724" s="2"/>
       <c r="AE724" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF724" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AG724" t="s" s="2">
-        <v>197</v>
+        <v>1128</v>
       </c>
       <c r="AH724" t="s" s="2">
         <v>76</v>
@@ -81623,7 +81605,7 @@
         <v>75</v>
       </c>
       <c r="AK724" t="s" s="2">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="725">
@@ -81631,12 +81613,14 @@
         <v>1258</v>
       </c>
       <c r="B725" t="s" s="2">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="C725" t="s" s="2">
         <v>1128</v>
       </c>
-      <c r="D725" s="2"/>
+      <c r="D725" t="s" s="2">
+        <v>1132</v>
+      </c>
       <c r="E725" t="s" s="2">
         <v>75</v>
       </c>
@@ -81645,10 +81629,10 @@
         <v>76</v>
       </c>
       <c r="H725" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I725" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J725" t="s" s="2">
         <v>75</v>
@@ -81657,10 +81641,10 @@
         <v>75</v>
       </c>
       <c r="L725" t="s" s="2">
-        <v>205</v>
+        <v>1298</v>
       </c>
       <c r="M725" t="s" s="2">
-        <v>1129</v>
+        <v>1299</v>
       </c>
       <c r="N725" t="s" s="2">
         <v>1130</v>
@@ -81702,14 +81686,16 @@
         <v>75</v>
       </c>
       <c r="AC725" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="AD725" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AD725" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AE725" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF725" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AG725" t="s" s="2">
         <v>1128</v>
@@ -81732,13 +81718,13 @@
         <v>1258</v>
       </c>
       <c r="B726" t="s" s="2">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="C726" t="s" s="2">
         <v>1128</v>
       </c>
       <c r="D726" t="s" s="2">
-        <v>1132</v>
+        <v>210</v>
       </c>
       <c r="E726" t="s" s="2">
         <v>75</v>
@@ -81748,7 +81734,7 @@
         <v>76</v>
       </c>
       <c r="H726" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I726" t="s" s="2">
         <v>85</v>
@@ -81760,10 +81746,10 @@
         <v>75</v>
       </c>
       <c r="L726" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M726" t="s" s="2">
         <v>1300</v>
-      </c>
-      <c r="M726" t="s" s="2">
-        <v>1301</v>
       </c>
       <c r="N726" t="s" s="2">
         <v>1130</v>
@@ -81837,43 +81823,43 @@
         <v>1258</v>
       </c>
       <c r="B727" t="s" s="2">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="C727" t="s" s="2">
-        <v>1128</v>
-      </c>
-      <c r="D727" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>1136</v>
+      </c>
+      <c r="D727" s="2"/>
       <c r="E727" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F727" s="2"/>
       <c r="G727" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H727" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I727" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J727" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K727" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="L727" t="s" s="2">
-        <v>211</v>
+        <v>159</v>
       </c>
       <c r="M727" t="s" s="2">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="N727" t="s" s="2">
-        <v>1130</v>
-      </c>
-      <c r="O727" s="2"/>
+        <v>1138</v>
+      </c>
+      <c r="O727" t="s" s="2">
+        <v>1139</v>
+      </c>
       <c r="P727" s="2"/>
       <c r="Q727" t="s" s="2">
         <v>75</v>
@@ -81883,7 +81869,7 @@
         <v>75</v>
       </c>
       <c r="T727" t="s" s="2">
-        <v>75</v>
+        <v>1239</v>
       </c>
       <c r="U727" t="s" s="2">
         <v>75</v>
@@ -81898,13 +81884,13 @@
         <v>75</v>
       </c>
       <c r="Y727" t="s" s="2">
-        <v>75</v>
+        <v>216</v>
       </c>
       <c r="Z727" t="s" s="2">
-        <v>75</v>
+        <v>1140</v>
       </c>
       <c r="AA727" t="s" s="2">
-        <v>75</v>
+        <v>1141</v>
       </c>
       <c r="AB727" t="s" s="2">
         <v>75</v>
@@ -81922,13 +81908,13 @@
         <v>75</v>
       </c>
       <c r="AG727" t="s" s="2">
-        <v>1128</v>
+        <v>1136</v>
       </c>
       <c r="AH727" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI727" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ727" t="s" s="2">
         <v>75</v>
@@ -81942,10 +81928,10 @@
         <v>1258</v>
       </c>
       <c r="B728" t="s" s="2">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="C728" t="s" s="2">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="D728" s="2"/>
       <c r="E728" t="s" s="2">
@@ -81971,15 +81957,17 @@
         <v>159</v>
       </c>
       <c r="M728" t="s" s="2">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="N728" t="s" s="2">
-        <v>1138</v>
+        <v>1144</v>
       </c>
       <c r="O728" t="s" s="2">
-        <v>1139</v>
-      </c>
-      <c r="P728" s="2"/>
+        <v>1145</v>
+      </c>
+      <c r="P728" t="s" s="2">
+        <v>1146</v>
+      </c>
       <c r="Q728" t="s" s="2">
         <v>75</v>
       </c>
@@ -81988,7 +81976,7 @@
         <v>75</v>
       </c>
       <c r="T728" t="s" s="2">
-        <v>1239</v>
+        <v>1147</v>
       </c>
       <c r="U728" t="s" s="2">
         <v>75</v>
@@ -82006,10 +81994,10 @@
         <v>216</v>
       </c>
       <c r="Z728" t="s" s="2">
-        <v>1140</v>
+        <v>1148</v>
       </c>
       <c r="AA728" t="s" s="2">
-        <v>1141</v>
+        <v>1149</v>
       </c>
       <c r="AB728" t="s" s="2">
         <v>75</v>
@@ -82027,7 +82015,7 @@
         <v>75</v>
       </c>
       <c r="AG728" t="s" s="2">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="AH728" t="s" s="2">
         <v>84</v>
@@ -82047,10 +82035,10 @@
         <v>1258</v>
       </c>
       <c r="B729" t="s" s="2">
-        <v>1142</v>
+        <v>1150</v>
       </c>
       <c r="C729" t="s" s="2">
-        <v>1142</v>
+        <v>1150</v>
       </c>
       <c r="D729" s="2"/>
       <c r="E729" t="s" s="2">
@@ -82058,7 +82046,7 @@
       </c>
       <c r="F729" s="2"/>
       <c r="G729" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H729" t="s" s="2">
         <v>84</v>
@@ -82067,25 +82055,23 @@
         <v>85</v>
       </c>
       <c r="J729" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K729" t="s" s="2">
         <v>85</v>
       </c>
       <c r="L729" t="s" s="2">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="M729" t="s" s="2">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="N729" t="s" s="2">
-        <v>1144</v>
-      </c>
-      <c r="O729" t="s" s="2">
-        <v>1145</v>
-      </c>
+        <v>1152</v>
+      </c>
+      <c r="O729" s="2"/>
       <c r="P729" t="s" s="2">
-        <v>1146</v>
+        <v>1153</v>
       </c>
       <c r="Q729" t="s" s="2">
         <v>75</v>
@@ -82095,10 +82081,10 @@
         <v>75</v>
       </c>
       <c r="T729" t="s" s="2">
-        <v>1147</v>
+        <v>75</v>
       </c>
       <c r="U729" t="s" s="2">
-        <v>75</v>
+        <v>1154</v>
       </c>
       <c r="V729" t="s" s="2">
         <v>75</v>
@@ -82110,13 +82096,13 @@
         <v>75</v>
       </c>
       <c r="Y729" t="s" s="2">
-        <v>216</v>
+        <v>75</v>
       </c>
       <c r="Z729" t="s" s="2">
-        <v>1148</v>
+        <v>75</v>
       </c>
       <c r="AA729" t="s" s="2">
-        <v>1149</v>
+        <v>75</v>
       </c>
       <c r="AB729" t="s" s="2">
         <v>75</v>
@@ -82134,10 +82120,10 @@
         <v>75</v>
       </c>
       <c r="AG729" t="s" s="2">
-        <v>1142</v>
+        <v>1150</v>
       </c>
       <c r="AH729" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI729" t="s" s="2">
         <v>84</v>
@@ -82154,10 +82140,10 @@
         <v>1258</v>
       </c>
       <c r="B730" t="s" s="2">
-        <v>1150</v>
+        <v>1155</v>
       </c>
       <c r="C730" t="s" s="2">
-        <v>1150</v>
+        <v>1155</v>
       </c>
       <c r="D730" s="2"/>
       <c r="E730" t="s" s="2">
@@ -82165,7 +82151,7 @@
       </c>
       <c r="F730" s="2"/>
       <c r="G730" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H730" t="s" s="2">
         <v>84</v>
@@ -82180,17 +82166,19 @@
         <v>85</v>
       </c>
       <c r="L730" t="s" s="2">
-        <v>98</v>
+        <v>225</v>
       </c>
       <c r="M730" t="s" s="2">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="N730" t="s" s="2">
-        <v>1152</v>
-      </c>
-      <c r="O730" s="2"/>
+        <v>1157</v>
+      </c>
+      <c r="O730" t="s" s="2">
+        <v>1158</v>
+      </c>
       <c r="P730" t="s" s="2">
-        <v>1153</v>
+        <v>1159</v>
       </c>
       <c r="Q730" t="s" s="2">
         <v>75</v>
@@ -82200,10 +82188,10 @@
         <v>75</v>
       </c>
       <c r="T730" t="s" s="2">
-        <v>75</v>
+        <v>1305</v>
       </c>
       <c r="U730" t="s" s="2">
-        <v>1154</v>
+        <v>75</v>
       </c>
       <c r="V730" t="s" s="2">
         <v>75</v>
@@ -82215,13 +82203,11 @@
         <v>75</v>
       </c>
       <c r="Y730" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z730" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="Z730" s="2"/>
       <c r="AA730" t="s" s="2">
-        <v>75</v>
+        <v>1161</v>
       </c>
       <c r="AB730" t="s" s="2">
         <v>75</v>
@@ -82239,7 +82225,7 @@
         <v>75</v>
       </c>
       <c r="AG730" t="s" s="2">
-        <v>1150</v>
+        <v>1155</v>
       </c>
       <c r="AH730" t="s" s="2">
         <v>76</v>
@@ -82259,10 +82245,10 @@
         <v>1258</v>
       </c>
       <c r="B731" t="s" s="2">
-        <v>1155</v>
+        <v>1162</v>
       </c>
       <c r="C731" t="s" s="2">
-        <v>1155</v>
+        <v>1162</v>
       </c>
       <c r="D731" s="2"/>
       <c r="E731" t="s" s="2">
@@ -82285,19 +82271,19 @@
         <v>85</v>
       </c>
       <c r="L731" t="s" s="2">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="M731" t="s" s="2">
-        <v>1306</v>
+        <v>420</v>
       </c>
       <c r="N731" t="s" s="2">
-        <v>1157</v>
+        <v>1164</v>
       </c>
       <c r="O731" t="s" s="2">
-        <v>1158</v>
+        <v>1165</v>
       </c>
       <c r="P731" t="s" s="2">
-        <v>1159</v>
+        <v>1166</v>
       </c>
       <c r="Q731" t="s" s="2">
         <v>75</v>
@@ -82307,7 +82293,7 @@
         <v>75</v>
       </c>
       <c r="T731" t="s" s="2">
-        <v>1307</v>
+        <v>75</v>
       </c>
       <c r="U731" t="s" s="2">
         <v>75</v>
@@ -82322,11 +82308,13 @@
         <v>75</v>
       </c>
       <c r="Y731" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="Z731" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Z731" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AA731" t="s" s="2">
-        <v>1161</v>
+        <v>75</v>
       </c>
       <c r="AB731" t="s" s="2">
         <v>75</v>
@@ -82344,7 +82332,7 @@
         <v>75</v>
       </c>
       <c r="AG731" t="s" s="2">
-        <v>1155</v>
+        <v>1162</v>
       </c>
       <c r="AH731" t="s" s="2">
         <v>76</v>
@@ -82364,10 +82352,10 @@
         <v>1258</v>
       </c>
       <c r="B732" t="s" s="2">
-        <v>1162</v>
+        <v>1167</v>
       </c>
       <c r="C732" t="s" s="2">
-        <v>1162</v>
+        <v>1167</v>
       </c>
       <c r="D732" s="2"/>
       <c r="E732" t="s" s="2">
@@ -82375,35 +82363,31 @@
       </c>
       <c r="F732" s="2"/>
       <c r="G732" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H732" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I732" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J732" t="s" s="2">
         <v>75</v>
       </c>
       <c r="K732" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="L732" t="s" s="2">
-        <v>239</v>
+        <v>1168</v>
       </c>
       <c r="M732" t="s" s="2">
-        <v>420</v>
+        <v>1169</v>
       </c>
       <c r="N732" t="s" s="2">
-        <v>1164</v>
-      </c>
-      <c r="O732" t="s" s="2">
-        <v>1165</v>
-      </c>
-      <c r="P732" t="s" s="2">
-        <v>1166</v>
-      </c>
+        <v>1170</v>
+      </c>
+      <c r="O732" s="2"/>
+      <c r="P732" s="2"/>
       <c r="Q732" t="s" s="2">
         <v>75</v>
       </c>
@@ -82451,7 +82435,7 @@
         <v>75</v>
       </c>
       <c r="AG732" t="s" s="2">
-        <v>1162</v>
+        <v>1167</v>
       </c>
       <c r="AH732" t="s" s="2">
         <v>76</v>
@@ -82471,10 +82455,10 @@
         <v>1258</v>
       </c>
       <c r="B733" t="s" s="2">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C733" t="s" s="2">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="D733" s="2"/>
       <c r="E733" t="s" s="2">
@@ -82482,31 +82466,35 @@
       </c>
       <c r="F733" s="2"/>
       <c r="G733" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H733" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="I733" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J733" t="s" s="2">
         <v>75</v>
       </c>
       <c r="K733" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="L733" t="s" s="2">
-        <v>1168</v>
+        <v>360</v>
       </c>
       <c r="M733" t="s" s="2">
-        <v>1169</v>
+        <v>1306</v>
       </c>
       <c r="N733" t="s" s="2">
-        <v>1170</v>
-      </c>
-      <c r="O733" s="2"/>
-      <c r="P733" s="2"/>
+        <v>1173</v>
+      </c>
+      <c r="O733" t="s" s="2">
+        <v>1174</v>
+      </c>
+      <c r="P733" t="s" s="2">
+        <v>1175</v>
+      </c>
       <c r="Q733" t="s" s="2">
         <v>75</v>
       </c>
@@ -82554,7 +82542,7 @@
         <v>75</v>
       </c>
       <c r="AG733" t="s" s="2">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="AH733" t="s" s="2">
         <v>76</v>
@@ -82574,14 +82562,14 @@
         <v>1258</v>
       </c>
       <c r="B734" t="s" s="2">
-        <v>1171</v>
+        <v>1176</v>
       </c>
       <c r="C734" t="s" s="2">
-        <v>1171</v>
+        <v>1176</v>
       </c>
       <c r="D734" s="2"/>
       <c r="E734" t="s" s="2">
-        <v>75</v>
+        <v>1177</v>
       </c>
       <c r="F734" s="2"/>
       <c r="G734" t="s" s="2">
@@ -82600,19 +82588,19 @@
         <v>85</v>
       </c>
       <c r="L734" t="s" s="2">
-        <v>360</v>
+        <v>1307</v>
       </c>
       <c r="M734" t="s" s="2">
         <v>1308</v>
       </c>
       <c r="N734" t="s" s="2">
-        <v>1173</v>
+        <v>1180</v>
       </c>
       <c r="O734" t="s" s="2">
-        <v>1174</v>
+        <v>1181</v>
       </c>
       <c r="P734" t="s" s="2">
-        <v>1175</v>
+        <v>1182</v>
       </c>
       <c r="Q734" t="s" s="2">
         <v>75</v>
@@ -82661,7 +82649,7 @@
         <v>75</v>
       </c>
       <c r="AG734" t="s" s="2">
-        <v>1171</v>
+        <v>1176</v>
       </c>
       <c r="AH734" t="s" s="2">
         <v>76</v>
@@ -82681,46 +82669,42 @@
         <v>1258</v>
       </c>
       <c r="B735" t="s" s="2">
-        <v>1176</v>
+        <v>1309</v>
       </c>
       <c r="C735" t="s" s="2">
-        <v>1176</v>
+        <v>1309</v>
       </c>
       <c r="D735" s="2"/>
       <c r="E735" t="s" s="2">
-        <v>1177</v>
+        <v>75</v>
       </c>
       <c r="F735" s="2"/>
       <c r="G735" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H735" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I735" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J735" t="s" s="2">
         <v>75</v>
       </c>
       <c r="K735" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="L735" t="s" s="2">
-        <v>1309</v>
+        <v>98</v>
       </c>
       <c r="M735" t="s" s="2">
-        <v>1310</v>
+        <v>99</v>
       </c>
       <c r="N735" t="s" s="2">
-        <v>1180</v>
-      </c>
-      <c r="O735" t="s" s="2">
-        <v>1181</v>
-      </c>
-      <c r="P735" t="s" s="2">
-        <v>1182</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="O735" s="2"/>
+      <c r="P735" s="2"/>
       <c r="Q735" t="s" s="2">
         <v>75</v>
       </c>
@@ -82768,7 +82752,7 @@
         <v>75</v>
       </c>
       <c r="AG735" t="s" s="2">
-        <v>1176</v>
+        <v>101</v>
       </c>
       <c r="AH735" t="s" s="2">
         <v>76</v>
@@ -82780,7 +82764,7 @@
         <v>75</v>
       </c>
       <c r="AK735" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
     </row>
     <row r="736">
@@ -82788,21 +82772,21 @@
         <v>1258</v>
       </c>
       <c r="B736" t="s" s="2">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="C736" t="s" s="2">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="D736" s="2"/>
       <c r="E736" t="s" s="2">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="F736" s="2"/>
       <c r="G736" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H736" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I736" t="s" s="2">
         <v>75</v>
@@ -82814,15 +82798,17 @@
         <v>75</v>
       </c>
       <c r="L736" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="M736" t="s" s="2">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="N736" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="O736" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="O736" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P736" s="2"/>
       <c r="Q736" t="s" s="2">
         <v>75</v>
@@ -82859,31 +82845,31 @@
         <v>75</v>
       </c>
       <c r="AC736" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="AD736" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AE736" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF736" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AG736" t="s" s="2">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="AH736" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI736" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ736" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK736" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
     </row>
     <row r="737">
@@ -82891,21 +82877,23 @@
         <v>1258</v>
       </c>
       <c r="B737" t="s" s="2">
+        <v>1311</v>
+      </c>
+      <c r="C737" t="s" s="2">
+        <v>1310</v>
+      </c>
+      <c r="D737" t="s" s="2">
         <v>1312</v>
       </c>
-      <c r="C737" t="s" s="2">
-        <v>1312</v>
-      </c>
-      <c r="D737" s="2"/>
       <c r="E737" t="s" s="2">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="F737" s="2"/>
       <c r="G737" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H737" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I737" t="s" s="2">
         <v>75</v>
@@ -82917,17 +82905,15 @@
         <v>75</v>
       </c>
       <c r="L737" t="s" s="2">
-        <v>104</v>
+        <v>1313</v>
       </c>
       <c r="M737" t="s" s="2">
-        <v>105</v>
+        <v>1314</v>
       </c>
       <c r="N737" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O737" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>1315</v>
+      </c>
+      <c r="O737" s="2"/>
       <c r="P737" s="2"/>
       <c r="Q737" t="s" s="2">
         <v>75</v>
@@ -82964,16 +82950,16 @@
         <v>75</v>
       </c>
       <c r="AC737" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AD737" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AE737" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF737" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AG737" t="s" s="2">
         <v>111</v>
@@ -82996,14 +82982,12 @@
         <v>1258</v>
       </c>
       <c r="B738" t="s" s="2">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="C738" t="s" s="2">
-        <v>1312</v>
-      </c>
-      <c r="D738" t="s" s="2">
-        <v>1314</v>
-      </c>
+        <v>1317</v>
+      </c>
+      <c r="D738" s="2"/>
       <c r="E738" t="s" s="2">
         <v>75</v>
       </c>
@@ -83024,13 +83008,13 @@
         <v>75</v>
       </c>
       <c r="L738" t="s" s="2">
-        <v>1315</v>
+        <v>98</v>
       </c>
       <c r="M738" t="s" s="2">
-        <v>1316</v>
+        <v>99</v>
       </c>
       <c r="N738" t="s" s="2">
-        <v>1317</v>
+        <v>100</v>
       </c>
       <c r="O738" s="2"/>
       <c r="P738" s="2"/>
@@ -83081,19 +83065,19 @@
         <v>75</v>
       </c>
       <c r="AG738" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AH738" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI738" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ738" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK738" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
     </row>
     <row r="739">
@@ -83115,7 +83099,7 @@
         <v>76</v>
       </c>
       <c r="H739" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I739" t="s" s="2">
         <v>75</v>
@@ -83127,13 +83111,13 @@
         <v>75</v>
       </c>
       <c r="L739" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="M739" t="s" s="2">
-        <v>99</v>
+        <v>182</v>
       </c>
       <c r="N739" t="s" s="2">
-        <v>100</v>
+        <v>183</v>
       </c>
       <c r="O739" s="2"/>
       <c r="P739" s="2"/>
@@ -83172,31 +83156,31 @@
         <v>75</v>
       </c>
       <c r="AC739" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="AD739" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AE739" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF739" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AG739" t="s" s="2">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="AH739" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI739" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ739" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK739" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
     </row>
     <row r="740">
@@ -83215,10 +83199,10 @@
       </c>
       <c r="F740" s="2"/>
       <c r="G740" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H740" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="I740" t="s" s="2">
         <v>75</v>
@@ -83230,22 +83214,24 @@
         <v>75</v>
       </c>
       <c r="L740" t="s" s="2">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="M740" t="s" s="2">
-        <v>182</v>
+        <v>1002</v>
       </c>
       <c r="N740" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O740" s="2"/>
+        <v>1003</v>
+      </c>
+      <c r="O740" t="s" s="2">
+        <v>1004</v>
+      </c>
       <c r="P740" s="2"/>
       <c r="Q740" t="s" s="2">
         <v>75</v>
       </c>
       <c r="R740" s="2"/>
       <c r="S740" t="s" s="2">
-        <v>75</v>
+        <v>1322</v>
       </c>
       <c r="T740" t="s" s="2">
         <v>75</v>
@@ -83275,31 +83261,31 @@
         <v>75</v>
       </c>
       <c r="AC740" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AD740" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AE740" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF740" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AG740" t="s" s="2">
-        <v>111</v>
+        <v>1001</v>
       </c>
       <c r="AH740" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI740" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ740" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK740" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
     </row>
     <row r="741">
@@ -83307,10 +83293,10 @@
         <v>1258</v>
       </c>
       <c r="B741" t="s" s="2">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="C741" t="s" s="2">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="D741" s="2"/>
       <c r="E741" t="s" s="2">
@@ -83333,24 +83319,22 @@
         <v>75</v>
       </c>
       <c r="L741" t="s" s="2">
-        <v>125</v>
+        <v>1325</v>
       </c>
       <c r="M741" t="s" s="2">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="N741" t="s" s="2">
-        <v>1003</v>
-      </c>
-      <c r="O741" t="s" s="2">
-        <v>1004</v>
-      </c>
+        <v>1008</v>
+      </c>
+      <c r="O741" s="2"/>
       <c r="P741" s="2"/>
       <c r="Q741" t="s" s="2">
         <v>75</v>
       </c>
       <c r="R741" s="2"/>
       <c r="S741" t="s" s="2">
-        <v>1324</v>
+        <v>75</v>
       </c>
       <c r="T741" t="s" s="2">
         <v>75</v>
@@ -83392,10 +83376,10 @@
         <v>75</v>
       </c>
       <c r="AG741" t="s" s="2">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="AH741" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI741" t="s" s="2">
         <v>84</v>
@@ -83404,7 +83388,7 @@
         <v>75</v>
       </c>
       <c r="AK741" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
     </row>
     <row r="742">
@@ -83412,7 +83396,7 @@
         <v>1258</v>
       </c>
       <c r="B742" t="s" s="2">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="C742" t="s" s="2">
         <v>1326</v>
@@ -83423,7 +83407,7 @@
       </c>
       <c r="F742" s="2"/>
       <c r="G742" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H742" t="s" s="2">
         <v>84</v>
@@ -83435,18 +83419,20 @@
         <v>75</v>
       </c>
       <c r="K742" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="L742" t="s" s="2">
-        <v>1327</v>
+        <v>98</v>
       </c>
       <c r="M742" t="s" s="2">
-        <v>1007</v>
+        <v>425</v>
       </c>
       <c r="N742" t="s" s="2">
-        <v>1008</v>
-      </c>
-      <c r="O742" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="O742" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="P742" s="2"/>
       <c r="Q742" t="s" s="2">
         <v>75</v>
@@ -83495,7 +83481,7 @@
         <v>75</v>
       </c>
       <c r="AG742" t="s" s="2">
-        <v>1005</v>
+        <v>428</v>
       </c>
       <c r="AH742" t="s" s="2">
         <v>76</v>
@@ -83504,7 +83490,7 @@
         <v>84</v>
       </c>
       <c r="AJ742" t="s" s="2">
-        <v>75</v>
+        <v>429</v>
       </c>
       <c r="AK742" t="s" s="2">
         <v>96</v>
@@ -83515,10 +83501,10 @@
         <v>1258</v>
       </c>
       <c r="B743" t="s" s="2">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="C743" t="s" s="2">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="D743" s="2"/>
       <c r="E743" t="s" s="2">
@@ -83541,16 +83527,16 @@
         <v>85</v>
       </c>
       <c r="L743" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="M743" t="s" s="2">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="N743" t="s" s="2">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="O743" t="s" s="2">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="P743" s="2"/>
       <c r="Q743" t="s" s="2">
@@ -83576,13 +83562,13 @@
         <v>75</v>
       </c>
       <c r="Y743" t="s" s="2">
-        <v>75</v>
+        <v>141</v>
       </c>
       <c r="Z743" t="s" s="2">
-        <v>75</v>
+        <v>434</v>
       </c>
       <c r="AA743" t="s" s="2">
-        <v>75</v>
+        <v>435</v>
       </c>
       <c r="AB743" t="s" s="2">
         <v>75</v>
@@ -83600,7 +83586,7 @@
         <v>75</v>
       </c>
       <c r="AG743" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="AH743" t="s" s="2">
         <v>76</v>
@@ -83609,7 +83595,7 @@
         <v>84</v>
       </c>
       <c r="AJ743" t="s" s="2">
-        <v>429</v>
+        <v>75</v>
       </c>
       <c r="AK743" t="s" s="2">
         <v>96</v>
@@ -83620,10 +83606,10 @@
         <v>1258</v>
       </c>
       <c r="B744" t="s" s="2">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="C744" t="s" s="2">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="D744" s="2"/>
       <c r="E744" t="s" s="2">
@@ -83646,16 +83632,16 @@
         <v>85</v>
       </c>
       <c r="L744" t="s" s="2">
-        <v>125</v>
+        <v>205</v>
       </c>
       <c r="M744" t="s" s="2">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="N744" t="s" s="2">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="O744" t="s" s="2">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="P744" s="2"/>
       <c r="Q744" t="s" s="2">
@@ -83681,13 +83667,13 @@
         <v>75</v>
       </c>
       <c r="Y744" t="s" s="2">
-        <v>141</v>
+        <v>75</v>
       </c>
       <c r="Z744" t="s" s="2">
-        <v>434</v>
+        <v>75</v>
       </c>
       <c r="AA744" t="s" s="2">
-        <v>435</v>
+        <v>75</v>
       </c>
       <c r="AB744" t="s" s="2">
         <v>75</v>
@@ -83705,7 +83691,7 @@
         <v>75</v>
       </c>
       <c r="AG744" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="AH744" t="s" s="2">
         <v>76</v>
@@ -83725,10 +83711,10 @@
         <v>1258</v>
       </c>
       <c r="B745" t="s" s="2">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C745" t="s" s="2">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D745" s="2"/>
       <c r="E745" t="s" s="2">
@@ -83751,16 +83737,16 @@
         <v>85</v>
       </c>
       <c r="L745" t="s" s="2">
-        <v>205</v>
+        <v>98</v>
       </c>
       <c r="M745" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="N745" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="O745" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="P745" s="2"/>
       <c r="Q745" t="s" s="2">
@@ -83810,7 +83796,7 @@
         <v>75</v>
       </c>
       <c r="AG745" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AH745" t="s" s="2">
         <v>76</v>
@@ -83830,10 +83816,10 @@
         <v>1258</v>
       </c>
       <c r="B746" t="s" s="2">
-        <v>1331</v>
+        <v>1183</v>
       </c>
       <c r="C746" t="s" s="2">
-        <v>1331</v>
+        <v>1183</v>
       </c>
       <c r="D746" s="2"/>
       <c r="E746" t="s" s="2">
@@ -83844,7 +83830,7 @@
         <v>76</v>
       </c>
       <c r="H746" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I746" t="s" s="2">
         <v>75</v>
@@ -83853,21 +83839,23 @@
         <v>75</v>
       </c>
       <c r="K746" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="L746" t="s" s="2">
-        <v>98</v>
+        <v>225</v>
       </c>
       <c r="M746" t="s" s="2">
-        <v>443</v>
+        <v>1184</v>
       </c>
       <c r="N746" t="s" s="2">
-        <v>444</v>
+        <v>1185</v>
       </c>
       <c r="O746" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="P746" s="2"/>
+        <v>1186</v>
+      </c>
+      <c r="P746" t="s" s="2">
+        <v>1187</v>
+      </c>
       <c r="Q746" t="s" s="2">
         <v>75</v>
       </c>
@@ -83891,13 +83879,13 @@
         <v>75</v>
       </c>
       <c r="Y746" t="s" s="2">
-        <v>75</v>
+        <v>163</v>
       </c>
       <c r="Z746" t="s" s="2">
-        <v>75</v>
+        <v>1188</v>
       </c>
       <c r="AA746" t="s" s="2">
-        <v>75</v>
+        <v>1189</v>
       </c>
       <c r="AB746" t="s" s="2">
         <v>75</v>
@@ -83915,7 +83903,7 @@
         <v>75</v>
       </c>
       <c r="AG746" t="s" s="2">
-        <v>446</v>
+        <v>1183</v>
       </c>
       <c r="AH746" t="s" s="2">
         <v>76</v>
@@ -83935,10 +83923,10 @@
         <v>1258</v>
       </c>
       <c r="B747" t="s" s="2">
-        <v>1183</v>
+        <v>1190</v>
       </c>
       <c r="C747" t="s" s="2">
-        <v>1183</v>
+        <v>1190</v>
       </c>
       <c r="D747" s="2"/>
       <c r="E747" t="s" s="2">
@@ -83949,7 +83937,7 @@
         <v>76</v>
       </c>
       <c r="H747" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="I747" t="s" s="2">
         <v>75</v>
@@ -83961,20 +83949,16 @@
         <v>75</v>
       </c>
       <c r="L747" t="s" s="2">
-        <v>225</v>
+        <v>1191</v>
       </c>
       <c r="M747" t="s" s="2">
-        <v>1184</v>
+        <v>1330</v>
       </c>
       <c r="N747" t="s" s="2">
-        <v>1185</v>
-      </c>
-      <c r="O747" t="s" s="2">
-        <v>1186</v>
-      </c>
-      <c r="P747" t="s" s="2">
-        <v>1187</v>
-      </c>
+        <v>1193</v>
+      </c>
+      <c r="O747" s="2"/>
+      <c r="P747" s="2"/>
       <c r="Q747" t="s" s="2">
         <v>75</v>
       </c>
@@ -83998,13 +83982,13 @@
         <v>75</v>
       </c>
       <c r="Y747" t="s" s="2">
-        <v>163</v>
+        <v>75</v>
       </c>
       <c r="Z747" t="s" s="2">
-        <v>1188</v>
+        <v>75</v>
       </c>
       <c r="AA747" t="s" s="2">
-        <v>1189</v>
+        <v>75</v>
       </c>
       <c r="AB747" t="s" s="2">
         <v>75</v>
@@ -84022,13 +84006,13 @@
         <v>75</v>
       </c>
       <c r="AG747" t="s" s="2">
-        <v>1183</v>
+        <v>1190</v>
       </c>
       <c r="AH747" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI747" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ747" t="s" s="2">
         <v>75</v>
@@ -84042,10 +84026,10 @@
         <v>1258</v>
       </c>
       <c r="B748" t="s" s="2">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="C748" t="s" s="2">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="D748" s="2"/>
       <c r="E748" t="s" s="2">
@@ -84056,7 +84040,7 @@
         <v>76</v>
       </c>
       <c r="H748" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I748" t="s" s="2">
         <v>75</v>
@@ -84068,15 +84052,17 @@
         <v>75</v>
       </c>
       <c r="L748" t="s" s="2">
-        <v>1191</v>
+        <v>263</v>
       </c>
       <c r="M748" t="s" s="2">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="N748" t="s" s="2">
-        <v>1193</v>
-      </c>
-      <c r="O748" s="2"/>
+        <v>1196</v>
+      </c>
+      <c r="O748" t="s" s="2">
+        <v>1197</v>
+      </c>
       <c r="P748" s="2"/>
       <c r="Q748" t="s" s="2">
         <v>75</v>
@@ -84125,7 +84111,7 @@
         <v>75</v>
       </c>
       <c r="AG748" t="s" s="2">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="AH748" t="s" s="2">
         <v>76</v>
@@ -84134,7 +84120,7 @@
         <v>77</v>
       </c>
       <c r="AJ748" t="s" s="2">
-        <v>75</v>
+        <v>1198</v>
       </c>
       <c r="AK748" t="s" s="2">
         <v>96</v>
@@ -84145,10 +84131,10 @@
         <v>1258</v>
       </c>
       <c r="B749" t="s" s="2">
-        <v>1194</v>
+        <v>1199</v>
       </c>
       <c r="C749" t="s" s="2">
-        <v>1194</v>
+        <v>1199</v>
       </c>
       <c r="D749" s="2"/>
       <c r="E749" t="s" s="2">
@@ -84159,7 +84145,7 @@
         <v>76</v>
       </c>
       <c r="H749" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I749" t="s" s="2">
         <v>75</v>
@@ -84171,17 +84157,15 @@
         <v>75</v>
       </c>
       <c r="L749" t="s" s="2">
-        <v>263</v>
+        <v>98</v>
       </c>
       <c r="M749" t="s" s="2">
-        <v>1333</v>
+        <v>99</v>
       </c>
       <c r="N749" t="s" s="2">
-        <v>1196</v>
-      </c>
-      <c r="O749" t="s" s="2">
-        <v>1197</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="O749" s="2"/>
       <c r="P749" s="2"/>
       <c r="Q749" t="s" s="2">
         <v>75</v>
@@ -84230,19 +84214,19 @@
         <v>75</v>
       </c>
       <c r="AG749" t="s" s="2">
-        <v>1194</v>
+        <v>101</v>
       </c>
       <c r="AH749" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI749" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ749" t="s" s="2">
-        <v>1198</v>
+        <v>75</v>
       </c>
       <c r="AK749" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
     </row>
     <row r="750">
@@ -84250,21 +84234,21 @@
         <v>1258</v>
       </c>
       <c r="B750" t="s" s="2">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="C750" t="s" s="2">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="D750" s="2"/>
       <c r="E750" t="s" s="2">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="F750" s="2"/>
       <c r="G750" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H750" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I750" t="s" s="2">
         <v>75</v>
@@ -84276,15 +84260,17 @@
         <v>75</v>
       </c>
       <c r="L750" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="M750" t="s" s="2">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="N750" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="O750" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="O750" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P750" s="2"/>
       <c r="Q750" t="s" s="2">
         <v>75</v>
@@ -84333,19 +84319,19 @@
         <v>75</v>
       </c>
       <c r="AG750" t="s" s="2">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="AH750" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI750" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ750" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK750" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
     </row>
     <row r="751">
@@ -84353,14 +84339,14 @@
         <v>1258</v>
       </c>
       <c r="B751" t="s" s="2">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="C751" t="s" s="2">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="D751" s="2"/>
       <c r="E751" t="s" s="2">
-        <v>103</v>
+        <v>271</v>
       </c>
       <c r="F751" s="2"/>
       <c r="G751" t="s" s="2">
@@ -84373,24 +84359,26 @@
         <v>75</v>
       </c>
       <c r="J751" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K751" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="L751" t="s" s="2">
         <v>104</v>
       </c>
       <c r="M751" t="s" s="2">
-        <v>105</v>
+        <v>272</v>
       </c>
       <c r="N751" t="s" s="2">
-        <v>106</v>
+        <v>273</v>
       </c>
       <c r="O751" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="P751" s="2"/>
+      <c r="P751" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="Q751" t="s" s="2">
         <v>75</v>
       </c>
@@ -84438,7 +84426,7 @@
         <v>75</v>
       </c>
       <c r="AG751" t="s" s="2">
-        <v>111</v>
+        <v>275</v>
       </c>
       <c r="AH751" t="s" s="2">
         <v>76</v>
@@ -84458,45 +84446,45 @@
         <v>1258</v>
       </c>
       <c r="B752" t="s" s="2">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="C752" t="s" s="2">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="D752" s="2"/>
       <c r="E752" t="s" s="2">
-        <v>271</v>
+        <v>75</v>
       </c>
       <c r="F752" s="2"/>
       <c r="G752" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H752" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I752" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J752" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K752" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="L752" t="s" s="2">
-        <v>104</v>
+        <v>225</v>
       </c>
       <c r="M752" t="s" s="2">
-        <v>272</v>
+        <v>1203</v>
       </c>
       <c r="N752" t="s" s="2">
-        <v>273</v>
+        <v>1204</v>
       </c>
       <c r="O752" t="s" s="2">
-        <v>107</v>
+        <v>1205</v>
       </c>
       <c r="P752" t="s" s="2">
-        <v>274</v>
+        <v>1206</v>
       </c>
       <c r="Q752" t="s" s="2">
         <v>75</v>
@@ -84521,13 +84509,13 @@
         <v>75</v>
       </c>
       <c r="Y752" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="Z752" t="s" s="2">
-        <v>75</v>
+        <v>1207</v>
       </c>
       <c r="AA752" t="s" s="2">
-        <v>75</v>
+        <v>1208</v>
       </c>
       <c r="AB752" t="s" s="2">
         <v>75</v>
@@ -84545,19 +84533,19 @@
         <v>75</v>
       </c>
       <c r="AG752" t="s" s="2">
-        <v>275</v>
+        <v>1202</v>
       </c>
       <c r="AH752" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI752" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ752" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK752" t="s" s="2">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="753">
@@ -84565,10 +84553,10 @@
         <v>1258</v>
       </c>
       <c r="B753" t="s" s="2">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="C753" t="s" s="2">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="D753" s="2"/>
       <c r="E753" t="s" s="2">
@@ -84585,30 +84573,32 @@
         <v>75</v>
       </c>
       <c r="J753" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K753" t="s" s="2">
         <v>75</v>
       </c>
       <c r="L753" t="s" s="2">
-        <v>225</v>
+        <v>532</v>
       </c>
       <c r="M753" t="s" s="2">
-        <v>1203</v>
+        <v>1210</v>
       </c>
       <c r="N753" t="s" s="2">
-        <v>1204</v>
+        <v>1211</v>
       </c>
       <c r="O753" t="s" s="2">
-        <v>1205</v>
+        <v>1212</v>
       </c>
       <c r="P753" t="s" s="2">
-        <v>1206</v>
+        <v>1213</v>
       </c>
       <c r="Q753" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="R753" s="2"/>
+      <c r="R753" t="s" s="2">
+        <v>1214</v>
+      </c>
       <c r="S753" t="s" s="2">
         <v>75</v>
       </c>
@@ -84628,13 +84618,13 @@
         <v>75</v>
       </c>
       <c r="Y753" t="s" s="2">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="Z753" t="s" s="2">
-        <v>1207</v>
+        <v>75</v>
       </c>
       <c r="AA753" t="s" s="2">
-        <v>1208</v>
+        <v>75</v>
       </c>
       <c r="AB753" t="s" s="2">
         <v>75</v>
@@ -84652,7 +84642,7 @@
         <v>75</v>
       </c>
       <c r="AG753" t="s" s="2">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="AH753" t="s" s="2">
         <v>76</v>
@@ -84661,7 +84651,7 @@
         <v>84</v>
       </c>
       <c r="AJ753" t="s" s="2">
-        <v>75</v>
+        <v>1215</v>
       </c>
       <c r="AK753" t="s" s="2">
         <v>96</v>
@@ -84672,10 +84662,10 @@
         <v>1258</v>
       </c>
       <c r="B754" t="s" s="2">
-        <v>1209</v>
+        <v>1216</v>
       </c>
       <c r="C754" t="s" s="2">
-        <v>1209</v>
+        <v>1216</v>
       </c>
       <c r="D754" s="2"/>
       <c r="E754" t="s" s="2">
@@ -84692,32 +84682,28 @@
         <v>75</v>
       </c>
       <c r="J754" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K754" t="s" s="2">
         <v>75</v>
       </c>
       <c r="L754" t="s" s="2">
-        <v>532</v>
+        <v>360</v>
       </c>
       <c r="M754" t="s" s="2">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="N754" t="s" s="2">
-        <v>1211</v>
-      </c>
-      <c r="O754" t="s" s="2">
-        <v>1212</v>
-      </c>
+        <v>1218</v>
+      </c>
+      <c r="O754" s="2"/>
       <c r="P754" t="s" s="2">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="Q754" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="R754" t="s" s="2">
-        <v>1214</v>
-      </c>
+      <c r="R754" s="2"/>
       <c r="S754" t="s" s="2">
         <v>75</v>
       </c>
@@ -84761,7 +84747,7 @@
         <v>75</v>
       </c>
       <c r="AG754" t="s" s="2">
-        <v>1209</v>
+        <v>1216</v>
       </c>
       <c r="AH754" t="s" s="2">
         <v>76</v>
@@ -84770,7 +84756,7 @@
         <v>84</v>
       </c>
       <c r="AJ754" t="s" s="2">
-        <v>1215</v>
+        <v>75</v>
       </c>
       <c r="AK754" t="s" s="2">
         <v>96</v>
@@ -84781,10 +84767,10 @@
         <v>1258</v>
       </c>
       <c r="B755" t="s" s="2">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="C755" t="s" s="2">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="D755" s="2"/>
       <c r="E755" t="s" s="2">
@@ -84792,10 +84778,10 @@
       </c>
       <c r="F755" s="2"/>
       <c r="G755" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H755" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="I755" t="s" s="2">
         <v>75</v>
@@ -84807,18 +84793,16 @@
         <v>75</v>
       </c>
       <c r="L755" t="s" s="2">
-        <v>360</v>
+        <v>1332</v>
       </c>
       <c r="M755" t="s" s="2">
-        <v>1217</v>
+        <v>1333</v>
       </c>
       <c r="N755" t="s" s="2">
-        <v>1218</v>
+        <v>1223</v>
       </c>
       <c r="O755" s="2"/>
-      <c r="P755" t="s" s="2">
-        <v>1219</v>
-      </c>
+      <c r="P755" s="2"/>
       <c r="Q755" t="s" s="2">
         <v>75</v>
       </c>
@@ -84866,10 +84850,10 @@
         <v>75</v>
       </c>
       <c r="AG755" t="s" s="2">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="AH755" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI755" t="s" s="2">
         <v>84</v>
@@ -84886,10 +84870,10 @@
         <v>1258</v>
       </c>
       <c r="B756" t="s" s="2">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="C756" t="s" s="2">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D756" s="2"/>
       <c r="E756" t="s" s="2">
@@ -84897,10 +84881,10 @@
       </c>
       <c r="F756" s="2"/>
       <c r="G756" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H756" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I756" t="s" s="2">
         <v>75</v>
@@ -84912,16 +84896,20 @@
         <v>75</v>
       </c>
       <c r="L756" t="s" s="2">
-        <v>1334</v>
+        <v>225</v>
       </c>
       <c r="M756" t="s" s="2">
-        <v>1335</v>
+        <v>1225</v>
       </c>
       <c r="N756" t="s" s="2">
-        <v>1223</v>
-      </c>
-      <c r="O756" s="2"/>
-      <c r="P756" s="2"/>
+        <v>1226</v>
+      </c>
+      <c r="O756" t="s" s="2">
+        <v>1227</v>
+      </c>
+      <c r="P756" t="s" s="2">
+        <v>1228</v>
+      </c>
       <c r="Q756" t="s" s="2">
         <v>75</v>
       </c>
@@ -84945,13 +84933,13 @@
         <v>75</v>
       </c>
       <c r="Y756" t="s" s="2">
-        <v>75</v>
+        <v>163</v>
       </c>
       <c r="Z756" t="s" s="2">
-        <v>75</v>
+        <v>1229</v>
       </c>
       <c r="AA756" t="s" s="2">
-        <v>75</v>
+        <v>1230</v>
       </c>
       <c r="AB756" t="s" s="2">
         <v>75</v>
@@ -84969,125 +84957,18 @@
         <v>75</v>
       </c>
       <c r="AG756" t="s" s="2">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="AH756" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI756" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ756" t="s" s="2">
-        <v>75</v>
+        <v>1198</v>
       </c>
       <c r="AK756" t="s" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="757">
-      <c r="A757" t="s" s="2">
-        <v>1258</v>
-      </c>
-      <c r="B757" t="s" s="2">
-        <v>1224</v>
-      </c>
-      <c r="C757" t="s" s="2">
-        <v>1224</v>
-      </c>
-      <c r="D757" s="2"/>
-      <c r="E757" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F757" s="2"/>
-      <c r="G757" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H757" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I757" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J757" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K757" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="L757" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="M757" t="s" s="2">
-        <v>1225</v>
-      </c>
-      <c r="N757" t="s" s="2">
-        <v>1226</v>
-      </c>
-      <c r="O757" t="s" s="2">
-        <v>1227</v>
-      </c>
-      <c r="P757" t="s" s="2">
-        <v>1228</v>
-      </c>
-      <c r="Q757" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R757" s="2"/>
-      <c r="S757" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T757" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U757" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V757" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W757" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X757" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y757" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Z757" t="s" s="2">
-        <v>1229</v>
-      </c>
-      <c r="AA757" t="s" s="2">
-        <v>1230</v>
-      </c>
-      <c r="AB757" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC757" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD757" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE757" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF757" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG757" t="s" s="2">
-        <v>1224</v>
-      </c>
-      <c r="AH757" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI757" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ757" t="s" s="2">
-        <v>1198</v>
-      </c>
-      <c r="AK757" t="s" s="2">
         <v>96</v>
       </c>
     </row>

--- a/add-ext-deleted/ig/all-profiles.xlsx
+++ b/add-ext-deleted/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T15:53:21+00:00</t>
+    <t>2026-10-01T13:59:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-ext-deleted/ig/all-profiles.xlsx
+++ b/add-ext-deleted/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:59:48+00:00</t>
+    <t>2026-10-01T15:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-ext-deleted/ig/all-profiles.xlsx
+++ b/add-ext-deleted/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T15:54:53+00:00</t>
+    <t>2026-10-05T14:15:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-ext-deleted/ig/all-profiles.xlsx
+++ b/add-ext-deleted/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-05T14:15:07+00:00</t>
+    <t>2026-10-05T14:43:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-ext-deleted/ig/all-profiles.xlsx
+++ b/add-ext-deleted/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-05T14:43:16+00:00</t>
+    <t>2026-10-05T15:33:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-ext-deleted/ig/all-profiles.xlsx
+++ b/add-ext-deleted/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-05T15:33:11+00:00</t>
+    <t>2026-10-07T16:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-ext-deleted/ig/all-profiles.xlsx
+++ b/add-ext-deleted/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T16:07:50+00:00</t>
+    <t>2026-10-08T08:40:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
